--- a/backend/public/excel/order.xlsx
+++ b/backend/public/excel/order.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="38">
   <si>
     <t>No</t>
   </si>
@@ -89,6 +89,42 @@
   </si>
   <si>
     <t>16.650</t>
+  </si>
+  <si>
+    <t>ORD-1706941748360</t>
+  </si>
+  <si>
+    <t>89.000</t>
+  </si>
+  <si>
+    <t>9.790</t>
+  </si>
+  <si>
+    <t>98.790</t>
+  </si>
+  <si>
+    <t>Sate Kambing Muda</t>
+  </si>
+  <si>
+    <t>50.000</t>
+  </si>
+  <si>
+    <t>Kentang Goreng</t>
+  </si>
+  <si>
+    <t>12.000</t>
+  </si>
+  <si>
+    <t>24.000</t>
+  </si>
+  <si>
+    <t>ORD-1706941897337</t>
+  </si>
+  <si>
+    <t>5.500</t>
+  </si>
+  <si>
+    <t>55.500</t>
   </si>
 </sst>
 </file>
@@ -478,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -529,7 +565,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>45320.64841961805</v>
+        <v>45320</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -561,7 +597,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>45320.64841961805</v>
+        <v>45320</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -593,7 +629,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>45320.64841961805</v>
+        <v>45320</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -625,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>45320.71866378472</v>
+        <v>45320</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>23</v>
@@ -650,6 +686,134 @@
       </c>
       <c r="J5" s="2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45325</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>45325</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45325</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45325.27195601852</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
